--- a/results/models/summary_all_SA_sgAdaptive_b0_K20_t0.15_nomez_risk.xlsx
+++ b/results/models/summary_all_SA_sgAdaptive_b0_K20_t0.15_nomez_risk.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.047</v>
+        <v>0.167</v>
       </c>
       <c r="I2" t="n">
         <v>31.2952</v>
@@ -545,7 +545,7 @@
         <v>31.2952</v>
       </c>
       <c r="K2" t="n">
-        <v>6.0555</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>31.2952</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.052</v>
+        <v>0.15</v>
       </c>
       <c r="I3" t="n">
         <v>31.2952</v>
@@ -608,7 +608,7 @@
         <v>31.2952</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2532</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>31.2952</v>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.049</v>
+        <v>0.149</v>
       </c>
       <c r="I4" t="n">
         <v>31.2952</v>
@@ -671,7 +671,7 @@
         <v>31.2952</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6851</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>31.2952</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.05</v>
+        <v>0.142</v>
       </c>
       <c r="I5" t="n">
         <v>31.2952</v>
@@ -734,7 +734,7 @@
         <v>31.2952</v>
       </c>
       <c r="K5" t="n">
-        <v>9.7979</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>31.2952</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.049</v>
+        <v>0.177</v>
       </c>
       <c r="I6" t="n">
         <v>31.2952</v>
@@ -797,7 +797,7 @@
         <v>31.2952</v>
       </c>
       <c r="K6" t="n">
-        <v>9.8621</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>31.2952</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.04</v>
+        <v>0.147</v>
       </c>
       <c r="I7" t="n">
         <v>31.2952</v>
@@ -860,7 +860,7 @@
         <v>31.2952</v>
       </c>
       <c r="K7" t="n">
-        <v>9.321099999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>31.2952</v>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.041</v>
+        <v>0.146</v>
       </c>
       <c r="I8" t="n">
         <v>31.2952</v>
@@ -923,7 +923,7 @@
         <v>31.2952</v>
       </c>
       <c r="K8" t="n">
-        <v>7.1815</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>31.2952</v>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.042</v>
+        <v>0.141</v>
       </c>
       <c r="I9" t="n">
         <v>31.2952</v>
@@ -986,7 +986,7 @@
         <v>31.2952</v>
       </c>
       <c r="K9" t="n">
-        <v>7.2374</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>31.2952</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.044</v>
+        <v>0.149</v>
       </c>
       <c r="I10" t="n">
         <v>31.2952</v>
@@ -1049,7 +1049,7 @@
         <v>31.2952</v>
       </c>
       <c r="K10" t="n">
-        <v>7.7931</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>31.2952</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.054</v>
+        <v>0.151</v>
       </c>
       <c r="I11" t="n">
         <v>31.2952</v>
@@ -1112,7 +1112,7 @@
         <v>31.2952</v>
       </c>
       <c r="K11" t="n">
-        <v>10.5719</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>31.2952</v>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I12" t="n">
         <v>31.2952</v>
@@ -1175,7 +1175,7 @@
         <v>31.2952</v>
       </c>
       <c r="K12" t="n">
-        <v>10.7842</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>31.2952</v>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.041</v>
+        <v>0.2</v>
       </c>
       <c r="I13" t="n">
         <v>31.2952</v>
@@ -1238,7 +1238,7 @@
         <v>31.2952</v>
       </c>
       <c r="K13" t="n">
-        <v>9.8606</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>31.2952</v>
